--- a/data/mapas/Mapa_de_Carrera_Matematica.xlsx
+++ b/data/mapas/Mapa_de_Carrera_Matematica.xlsx
@@ -555,13 +555,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K59"/>
+  <dimension ref="A1:K44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="J2" s="5" t="n">
-        <v>49</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="J3" s="5">
-        <f>COUNTIF(B6:B59, "SI")</f>
+        <f>COUNTIF(B6:B44, "SI")</f>
         <v/>
       </c>
     </row>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="J4" s="5">
-        <f>COUNTIF(C6:C59, "SI")</f>
+        <f>COUNTIF(C6:C44, "SI")</f>
         <v/>
       </c>
     </row>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="J5" s="5">
-        <f>COUNTIF(F6:F59, "ADEUDA FINAL")</f>
+        <f>COUNTIF(F6:F44, "ADEUDA FINAL")</f>
         <v/>
       </c>
     </row>
@@ -710,14 +710,14 @@
         </is>
       </c>
       <c r="J6" s="12">
-        <f>COUNTIF(B6:B59, "SI")/49</f>
+        <f>COUNTIF(B6:B44, "SI")/35</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Análisis MATEMATICO I</t>
+          <t>Análisis Matemático I</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -753,14 +753,14 @@
         </is>
       </c>
       <c r="J7" s="12">
-        <f>COUNTIF(C6:C59, "SI")/49</f>
+        <f>COUNTIF(C6:C44, "SI")/35</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>ELEMENTOS Básica DE Matemática (Cuatr.)</t>
+          <t>Geometría I</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -794,7 +794,7 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>ELEMENTOS Básica DE Matemática</t>
+          <t>Introducción a la Matemática Superior</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -833,7 +833,7 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Geometria I</t>
+          <t>Elementos Básicos de Matemática</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
@@ -872,7 +872,7 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>INTR. A LA Matemática SUPERIOR</t>
+          <t>Pedagogía</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
@@ -911,7 +911,7 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>INTRODUCCION A LA Matemática SUPERIOR</t>
+          <t>Lectura, Escritura y Oralidad I (LEO 1)</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
@@ -950,7 +950,7 @@
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>Lectura, Escritura y Oralidad I (LEO 1)</t>
+          <t>Trabajo de Campo I</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
@@ -987,37 +987,10 @@
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>Pedagogía</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>1° Año</t>
-        </is>
-      </c>
-      <c r="E14" s="10">
-        <f>IF(B14="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F14" s="10">
-        <f>IF(C14="SI", "APROBADO", IF(B14="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G14" s="11">
-        <f>IF(C14="SI", "🟢 Aprobada", IF(B14="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>📌 2° AÑO</t>
+        </is>
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
@@ -1028,7 +1001,7 @@
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Psicología EDUCACIONAL</t>
+          <t>Álgebra II</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
@@ -1043,7 +1016,7 @@
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>1° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E15" s="10">
@@ -1067,7 +1040,7 @@
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>Psicología EDUCACIONAL (1° CUATR.)</t>
+          <t>Análisis Matemático II</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
@@ -1082,7 +1055,7 @@
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>1° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E16" s="10">
@@ -1101,7 +1074,7 @@
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Sujeto del Aprendizaje</t>
+          <t>Geometría II</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
@@ -1116,7 +1089,7 @@
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>1° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E17" s="10">
@@ -1135,7 +1108,7 @@
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Trabajo de Campo I</t>
+          <t>Física General</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
@@ -1150,7 +1123,7 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>1° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E18" s="10">
@@ -1169,7 +1142,7 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Trabajo de Campo I (cuatrimestral)</t>
+          <t>Didáctica General</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
@@ -1184,7 +1157,7 @@
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>1° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E19" s="10">
@@ -1200,17 +1173,44 @@
         <v/>
       </c>
     </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>📌 2° AÑO</t>
-        </is>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Psicología Educacional</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>2° Año</t>
+        </is>
+      </c>
+      <c r="E20" s="10">
+        <f>IF(B20="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F20" s="10">
+        <f>IF(C20="SI", "APROBADO", IF(B20="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G20" s="11">
+        <f>IF(C20="SI", "🟢 Aprobada", IF(B20="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Álgebra II</t>
+          <t>Sujetos de la Educación</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
@@ -1244,7 +1244,7 @@
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>Análisis MATEMATICO II</t>
+          <t>Trabajo de Campo II</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
@@ -1275,44 +1275,17 @@
         <v/>
       </c>
     </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>Didáctica GENERAL</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="inlineStr">
-        <is>
-          <t>2° Año</t>
-        </is>
-      </c>
-      <c r="E23" s="10">
-        <f>IF(B23="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F23" s="10">
-        <f>IF(C23="SI", "APROBADO", IF(B23="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G23" s="11">
-        <f>IF(C23="SI", "🟢 Aprobada", IF(B23="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>📌 3° AÑO</t>
+        </is>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>Filosofía</t>
+          <t>Álgebra III</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
@@ -1327,7 +1300,7 @@
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E24" s="10">
@@ -1346,7 +1319,7 @@
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>Física</t>
+          <t>Análisis Matemático III</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
@@ -1361,7 +1334,7 @@
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E25" s="10">
@@ -1380,7 +1353,7 @@
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Geometria II</t>
+          <t>Geometría III</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
@@ -1395,7 +1368,7 @@
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E26" s="10">
@@ -1414,7 +1387,7 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>Nuevas Tecnologias</t>
+          <t>Probabilidad y Estadística</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
@@ -1429,7 +1402,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E27" s="10">
@@ -1448,7 +1421,7 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>Trabajo de Campo II</t>
+          <t>Didáctica de la Matemática I</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
@@ -1463,7 +1436,7 @@
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E28" s="10">
@@ -1479,17 +1452,44 @@
         <v/>
       </c>
     </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>📌 3° AÑO</t>
-        </is>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>Historia Social de la Educación</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>3° Año</t>
+        </is>
+      </c>
+      <c r="E29" s="10">
+        <f>IF(B29="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F29" s="10">
+        <f>IF(C29="SI", "APROBADO", IF(B29="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G29" s="11">
+        <f>IF(C29="SI", "🟢 Aprobada", IF(B29="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>Álgebra III</t>
+          <t>Derechos Humanos, Sociedad y Estado</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
@@ -1523,7 +1523,7 @@
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>Derechos Humanos, SOCIEDAD Y ESTADO</t>
+          <t>Construcción de la Práctica Docente I</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
@@ -1554,44 +1554,17 @@
         <v/>
       </c>
     </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>Didáctica DE LA Matemática</t>
-        </is>
-      </c>
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C32" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="inlineStr">
-        <is>
-          <t>3° Año</t>
-        </is>
-      </c>
-      <c r="E32" s="10">
-        <f>IF(B32="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F32" s="10">
-        <f>IF(C32="SI", "APROBADO", IF(B32="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G32" s="11">
-        <f>IF(C32="SI", "🟢 Aprobada", IF(B32="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>📌 4° AÑO</t>
+        </is>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>HISTORIA DE LA Educación ARGENTINA</t>
+          <t>Fundamentos de la Matemática</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
@@ -1606,7 +1579,7 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E33" s="10">
@@ -1625,7 +1598,7 @@
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>HISTORIA DE LA Matemática</t>
+          <t>Ecuaciones Diferenciales</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
@@ -1640,7 +1613,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E34" s="10">
@@ -1659,7 +1632,7 @@
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>Probabilidad y Estadistica</t>
+          <t>Didáctica de la Matemática II</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
@@ -1674,7 +1647,7 @@
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E35" s="10">
@@ -1693,7 +1666,7 @@
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>Probabilidades y Estadistica</t>
+          <t>Historia de la Matemática</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
@@ -1708,7 +1681,7 @@
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E36" s="10">
@@ -1727,7 +1700,7 @@
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>TICS EN EL AULA DE Matemática</t>
+          <t>Tecnologías Digitales en la Enseñanza de la Matemática</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
@@ -1742,7 +1715,7 @@
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E37" s="10">
@@ -1761,7 +1734,7 @@
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>Trab. de Campo Iii. Const. Trab. Mat</t>
+          <t>Educación Sexual Integral (ESI)</t>
         </is>
       </c>
       <c r="B38" s="9" t="inlineStr">
@@ -1776,7 +1749,7 @@
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E38" s="10">
@@ -1795,7 +1768,7 @@
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>Trabajo de Campo III</t>
+          <t>Ética y Trabajo Docente</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
@@ -1810,7 +1783,7 @@
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E39" s="10">
@@ -1826,51 +1799,51 @@
         <v/>
       </c>
     </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>📌 4° AÑO</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="8" t="inlineStr">
-        <is>
-          <t>ASTRONOMIA GRAL. Básica</t>
-        </is>
-      </c>
-      <c r="B41" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C41" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D41" s="10" t="inlineStr">
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>Residencia y Construcción de la Práctica Docente II</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
         <is>
           <t>4° Año</t>
         </is>
       </c>
-      <c r="E41" s="10">
-        <f>IF(B41="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F41" s="10">
-        <f>IF(C41="SI", "APROBADO", IF(B41="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G41" s="11">
-        <f>IF(C41="SI", "🟢 Aprobada", IF(B41="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+      <c r="E40" s="10">
+        <f>IF(B40="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F40" s="10">
+        <f>IF(C40="SI", "APROBADO", IF(B40="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G40" s="11">
+        <f>IF(C40="SI", "🟢 Aprobada", IF(B40="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>📌 TRAMO SUPERIOR / SEMINARIOS</t>
+        </is>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>Construcción de la Práctica Docente</t>
+          <t>Seminario de Especialización en Matemática</t>
         </is>
       </c>
       <c r="B42" s="9" t="inlineStr">
@@ -1885,7 +1858,7 @@
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>Tramo Superior / Seminarios</t>
         </is>
       </c>
       <c r="E42" s="10">
@@ -1904,7 +1877,7 @@
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>Didáctica DE LA Matemática II</t>
+          <t>Epistemología de la Matemática</t>
         </is>
       </c>
       <c r="B43" s="9" t="inlineStr">
@@ -1919,7 +1892,7 @@
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>Tramo Superior / Seminarios</t>
         </is>
       </c>
       <c r="E43" s="10">
@@ -1938,7 +1911,7 @@
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>ECUACIONES DIFERENCIALES (1° Cuatrim)</t>
+          <t>Taller de Investigación Educativa en Matemática</t>
         </is>
       </c>
       <c r="B44" s="9" t="inlineStr">
@@ -1953,7 +1926,7 @@
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>Tramo Superior / Seminarios</t>
         </is>
       </c>
       <c r="E44" s="10">
@@ -1969,483 +1942,26 @@
         <v/>
       </c>
     </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="8" t="inlineStr">
-        <is>
-          <t>Educación SEXUAL INTEGRAL (1º CUATR.)</t>
-        </is>
-      </c>
-      <c r="B45" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C45" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D45" s="10" t="inlineStr">
-        <is>
-          <t>4° Año</t>
-        </is>
-      </c>
-      <c r="E45" s="10">
-        <f>IF(B45="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F45" s="10">
-        <f>IF(C45="SI", "APROBADO", IF(B45="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G45" s="11">
-        <f>IF(C45="SI", "🟢 Aprobada", IF(B45="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="8" t="inlineStr">
-        <is>
-          <t>FUNDAMENTOS DE LA Matemática</t>
-        </is>
-      </c>
-      <c r="B46" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C46" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D46" s="10" t="inlineStr">
-        <is>
-          <t>4° Año</t>
-        </is>
-      </c>
-      <c r="E46" s="10">
-        <f>IF(B46="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F46" s="10">
-        <f>IF(C46="SI", "APROBADO", IF(B46="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G46" s="11">
-        <f>IF(C46="SI", "🟢 Aprobada", IF(B46="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="8" t="inlineStr">
-        <is>
-          <t>Lengua Extranjera (cuatrimestral)</t>
-        </is>
-      </c>
-      <c r="B47" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C47" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D47" s="10" t="inlineStr">
-        <is>
-          <t>4° Año</t>
-        </is>
-      </c>
-      <c r="E47" s="10">
-        <f>IF(B47="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F47" s="10">
-        <f>IF(C47="SI", "APROBADO", IF(B47="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G47" s="11">
-        <f>IF(C47="SI", "🟢 Aprobada", IF(B47="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="8" t="inlineStr">
-        <is>
-          <t>Reflexion y Act. S/la Pract.doc. (1° Cuatr.)</t>
-        </is>
-      </c>
-      <c r="B48" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C48" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D48" s="10" t="inlineStr">
-        <is>
-          <t>4° Año</t>
-        </is>
-      </c>
-      <c r="E48" s="10">
-        <f>IF(B48="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F48" s="10">
-        <f>IF(C48="SI", "APROBADO", IF(B48="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G48" s="11">
-        <f>IF(C48="SI", "🟢 Aprobada", IF(B48="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="8" t="inlineStr">
-        <is>
-          <t>SISTEMA Y Política Educativa (1° CUATR.)</t>
-        </is>
-      </c>
-      <c r="B49" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C49" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D49" s="10" t="inlineStr">
-        <is>
-          <t>4° Año</t>
-        </is>
-      </c>
-      <c r="E49" s="10">
-        <f>IF(B49="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F49" s="10">
-        <f>IF(C49="SI", "APROBADO", IF(B49="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G49" s="11">
-        <f>IF(C49="SI", "🟢 Aprobada", IF(B49="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50" ht="22" customHeight="1">
-      <c r="A50" s="7" t="inlineStr">
-        <is>
-          <t>📌 5° AÑO (NIVEL SUPERIOR / TRAMO SUPERIOR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="8" t="inlineStr">
-        <is>
-          <t>Análisis MATEMÁTICO III</t>
-        </is>
-      </c>
-      <c r="B51" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C51" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D51" s="10" t="inlineStr">
-        <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
-        </is>
-      </c>
-      <c r="E51" s="10">
-        <f>IF(B51="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F51" s="10">
-        <f>IF(C51="SI", "APROBADO", IF(B51="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G51" s="11">
-        <f>IF(C51="SI", "🟢 Aprobada", IF(B51="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="8" t="inlineStr">
-        <is>
-          <t>CONSTRUCCION DE LA Práctica DOCENTE II</t>
-        </is>
-      </c>
-      <c r="B52" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C52" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D52" s="10" t="inlineStr">
-        <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
-        </is>
-      </c>
-      <c r="E52" s="10">
-        <f>IF(B52="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F52" s="10">
-        <f>IF(C52="SI", "APROBADO", IF(B52="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G52" s="11">
-        <f>IF(C52="SI", "🟢 Aprobada", IF(B52="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="8" t="inlineStr">
-        <is>
-          <t>FUNDAMENTOS DE LA Física</t>
-        </is>
-      </c>
-      <c r="B53" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C53" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D53" s="10" t="inlineStr">
-        <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
-        </is>
-      </c>
-      <c r="E53" s="10">
-        <f>IF(B53="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F53" s="10">
-        <f>IF(C53="SI", "APROBADO", IF(B53="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G53" s="11">
-        <f>IF(C53="SI", "🟢 Aprobada", IF(B53="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="8" t="inlineStr">
-        <is>
-          <t>TEMAS AVANZADOS DE Matemática</t>
-        </is>
-      </c>
-      <c r="B54" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C54" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D54" s="10" t="inlineStr">
-        <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
-        </is>
-      </c>
-      <c r="E54" s="10">
-        <f>IF(B54="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F54" s="10">
-        <f>IF(C54="SI", "APROBADO", IF(B54="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G54" s="11">
-        <f>IF(C54="SI", "🟢 Aprobada", IF(B54="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55" ht="22" customHeight="1">
-      <c r="A55" s="7" t="inlineStr">
-        <is>
-          <t>📌 6° AÑO (NIVEL SUPERIOR / TRAMO SUPERIOR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="8" t="inlineStr">
-        <is>
-          <t>Seminario de Especialización Superior II</t>
-        </is>
-      </c>
-      <c r="B56" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C56" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D56" s="10" t="inlineStr">
-        <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
-        </is>
-      </c>
-      <c r="E56" s="10">
-        <f>IF(B56="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F56" s="10">
-        <f>IF(C56="SI", "APROBADO", IF(B56="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G56" s="11">
-        <f>IF(C56="SI", "🟢 Aprobada", IF(B56="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="8" t="inlineStr">
-        <is>
-          <t>Tesis / Trabajo Final de Licenciatura</t>
-        </is>
-      </c>
-      <c r="B57" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C57" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D57" s="10" t="inlineStr">
-        <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
-        </is>
-      </c>
-      <c r="E57" s="10">
-        <f>IF(B57="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F57" s="10">
-        <f>IF(C57="SI", "APROBADO", IF(B57="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G57" s="11">
-        <f>IF(C57="SI", "🟢 Aprobada", IF(B57="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="8" t="inlineStr">
-        <is>
-          <t>Práctica de Nivel Superior II</t>
-        </is>
-      </c>
-      <c r="B58" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C58" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D58" s="10" t="inlineStr">
-        <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
-        </is>
-      </c>
-      <c r="E58" s="10">
-        <f>IF(B58="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F58" s="10">
-        <f>IF(C58="SI", "APROBADO", IF(B58="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G58" s="11">
-        <f>IF(C58="SI", "🟢 Aprobada", IF(B58="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="8" t="inlineStr">
-        <is>
-          <t>Acreditación de Residencia Superior</t>
-        </is>
-      </c>
-      <c r="B59" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C59" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D59" s="10" t="inlineStr">
-        <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
-        </is>
-      </c>
-      <c r="E59" s="10">
-        <f>IF(B59="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F59" s="10">
-        <f>IF(C59="SI", "APROBADO", IF(B59="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G59" s="11">
-        <f>IF(C59="SI", "🟢 Aprobada", IF(B59="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="15">
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A14:G14"/>
     <mergeCell ref="I12:J12"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A40:G40"/>
     <mergeCell ref="I15:J15"/>
     <mergeCell ref="I10:J10"/>
-    <mergeCell ref="A55:G55"/>
-    <mergeCell ref="A50:G50"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A20:G20"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A29:G29"/>
     <mergeCell ref="I13:J13"/>
     <mergeCell ref="I14:J14"/>
+    <mergeCell ref="A41:G41"/>
     <mergeCell ref="I9:J9"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A23:G23"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B16 B17 B18 B19 B21 B22 B23 B24 B25 B26 B27 B28 B30 B31 B32 B33 B34 B35 B36 B37 B38 B39 B41 B42 B43 B44 B45 B46 B47 B48 B49 B51 B52 B53 B54 B56 B57 B58 B59 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C21 C22 C23 C24 C25 C26 C27 C28 C30 C31 C32 C33 C34 C35 C36 C37 C38 C39 C41 C42 C43 C44 C45 C46 C47 C48 C49 C51 C52 C53 C54 C56 C57 C58 C59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
+    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B13 B15 B16 B17 B18 B19 B20 B21 B22 B24 B25 B26 B27 B28 B29 B30 B31 B33 B34 B35 B36 B37 B38 B39 B40 B42 B43 B44 C6 C7 C8 C9 C10 C11 C12 C13 C15 C16 C17 C18 C19 C20 C21 C22 C24 C25 C26 C27 C28 C29 C30 C31 C33 C34 C35 C36 C37 C38 C39 C40 C42 C43 C44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
       <formula1>"SI,NO"</formula1>
     </dataValidation>
   </dataValidations>

--- a/data/mapas/Mapa_de_Carrera_Matematica.xlsx
+++ b/data/mapas/Mapa_de_Carrera_Matematica.xlsx
@@ -555,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K44"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="J2" s="5" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="J3" s="5">
-        <f>COUNTIF(B6:B44, "SI")</f>
+        <f>COUNTIF(B6:B49, "SI")</f>
         <v/>
       </c>
     </row>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="J4" s="5">
-        <f>COUNTIF(C6:C44, "SI")</f>
+        <f>COUNTIF(C6:C49, "SI")</f>
         <v/>
       </c>
     </row>
@@ -667,14 +667,14 @@
         </is>
       </c>
       <c r="J5" s="5">
-        <f>COUNTIF(F6:F44, "ADEUDA FINAL")</f>
+        <f>COUNTIF(F6:F49, "ADEUDA FINAL")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Álgebra I</t>
+          <t>Elementos Básicos de Matemática</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -710,14 +710,14 @@
         </is>
       </c>
       <c r="J6" s="12">
-        <f>COUNTIF(B6:B44, "SI")/35</f>
+        <f>COUNTIF(B6:B49, "SI")/40</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Análisis Matemático I</t>
+          <t>Álgebra I</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="J7" s="12">
-        <f>COUNTIF(C6:C44, "SI")/35</f>
+        <f>COUNTIF(C6:C49, "SI")/40</f>
         <v/>
       </c>
     </row>
@@ -794,7 +794,7 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Introducción a la Matemática Superior</t>
+          <t>Análisis Matemático I</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -833,7 +833,7 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Elementos Básicos de Matemática</t>
+          <t>Introducción a la Matemática Superior</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
@@ -911,7 +911,7 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Lectura, Escritura y Oralidad I (LEO 1)</t>
+          <t>Psicología Educacional</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
@@ -950,7 +950,7 @@
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>Trabajo de Campo I</t>
+          <t>Sujeto del aprendizaje</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
@@ -987,10 +987,37 @@
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>📌 2° AÑO</t>
-        </is>
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Lectura, Escritura y Oralidad I (LEO 1)</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>1° Año</t>
+        </is>
+      </c>
+      <c r="E14" s="10">
+        <f>IF(B14="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F14" s="10">
+        <f>IF(C14="SI", "APROBADO", IF(B14="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G14" s="11">
+        <f>IF(C14="SI", "🟢 Aprobada", IF(B14="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
@@ -1001,7 +1028,7 @@
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Álgebra II</t>
+          <t>Trabajo de Campo I</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
@@ -1016,7 +1043,7 @@
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>1° Año</t>
         </is>
       </c>
       <c r="E15" s="10">
@@ -1037,44 +1064,17 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>Análisis Matemático II</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>2° Año</t>
-        </is>
-      </c>
-      <c r="E16" s="10">
-        <f>IF(B16="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F16" s="10">
-        <f>IF(C16="SI", "APROBADO", IF(B16="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G16" s="11">
-        <f>IF(C16="SI", "🟢 Aprobada", IF(B16="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>📌 2° AÑO</t>
+        </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Geometría II</t>
+          <t>Álgebra II</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
@@ -1108,7 +1108,7 @@
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Física General</t>
+          <t>Geometría II</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
@@ -1142,7 +1142,7 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Didáctica General</t>
+          <t>Análisis Matemático II</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
@@ -1176,7 +1176,7 @@
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Psicología Educacional</t>
+          <t>Física</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
@@ -1210,7 +1210,7 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Sujetos de la Educación</t>
+          <t>Nuevas tecnologías</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
@@ -1244,7 +1244,7 @@
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>Trabajo de Campo II</t>
+          <t>Filosofía</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
@@ -1275,17 +1275,44 @@
         <v/>
       </c>
     </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>📌 3° AÑO</t>
-        </is>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>Didáctica general</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>2° Año</t>
+        </is>
+      </c>
+      <c r="E23" s="10">
+        <f>IF(B23="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F23" s="10">
+        <f>IF(C23="SI", "APROBADO", IF(B23="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G23" s="11">
+        <f>IF(C23="SI", "🟢 Aprobada", IF(B23="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>Álgebra III</t>
+          <t>Trabajo de Campo II</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
@@ -1300,7 +1327,7 @@
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E24" s="10">
@@ -1316,44 +1343,17 @@
         <v/>
       </c>
     </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>Análisis Matemático III</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr">
-        <is>
-          <t>3° Año</t>
-        </is>
-      </c>
-      <c r="E25" s="10">
-        <f>IF(B25="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F25" s="10">
-        <f>IF(C25="SI", "APROBADO", IF(B25="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G25" s="11">
-        <f>IF(C25="SI", "🟢 Aprobada", IF(B25="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>📌 3° AÑO</t>
+        </is>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Geometría III</t>
+          <t>TICS en el aula de matemática</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
@@ -1387,7 +1387,7 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>Probabilidad y Estadística</t>
+          <t>Álgebra III</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>Didáctica de la Matemática I</t>
+          <t>Probabilidades y estadística</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
@@ -1455,7 +1455,7 @@
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>Historia Social de la Educación</t>
+          <t>Historia de la Matemática</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
@@ -1489,7 +1489,7 @@
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>Derechos Humanos, Sociedad y Estado</t>
+          <t>Historia de la Educación Argentina</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
@@ -1523,7 +1523,7 @@
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>Construcción de la Práctica Docente I</t>
+          <t>DDHH, Estado y Sociedad</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
@@ -1554,17 +1554,44 @@
         <v/>
       </c>
     </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>📌 4° AÑO</t>
-        </is>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>Didáctica de la Matemática 1</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>3° Año</t>
+        </is>
+      </c>
+      <c r="E32" s="10">
+        <f>IF(B32="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F32" s="10">
+        <f>IF(C32="SI", "APROBADO", IF(B32="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G32" s="11">
+        <f>IF(C32="SI", "🟢 Aprobada", IF(B32="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>Fundamentos de la Matemática</t>
+          <t>Lectura, Escritura y Oralidad II (LEO 2)</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
@@ -1579,7 +1606,7 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E33" s="10">
@@ -1598,7 +1625,7 @@
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>Ecuaciones Diferenciales</t>
+          <t>Trabajo de Campo III</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
@@ -1613,7 +1640,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E34" s="10">
@@ -1629,44 +1656,17 @@
         <v/>
       </c>
     </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="8" t="inlineStr">
-        <is>
-          <t>Didáctica de la Matemática II</t>
-        </is>
-      </c>
-      <c r="B35" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D35" s="10" t="inlineStr">
-        <is>
-          <t>4° Año</t>
-        </is>
-      </c>
-      <c r="E35" s="10">
-        <f>IF(B35="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F35" s="10">
-        <f>IF(C35="SI", "APROBADO", IF(B35="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G35" s="11">
-        <f>IF(C35="SI", "🟢 Aprobada", IF(B35="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>📌 4° AÑO</t>
+        </is>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>Historia de la Matemática</t>
+          <t>Fundamentos de la Matemática</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
@@ -1700,7 +1700,7 @@
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>Tecnologías Digitales en la Enseñanza de la Matemática</t>
+          <t>Astronomía General Básica</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
@@ -1734,7 +1734,7 @@
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>Educación Sexual Integral (ESI)</t>
+          <t>Lengua Extranjera</t>
         </is>
       </c>
       <c r="B38" s="9" t="inlineStr">
@@ -1768,7 +1768,7 @@
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>Ética y Trabajo Docente</t>
+          <t>Sistema y Política Educativa</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
@@ -1802,7 +1802,7 @@
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>Residencia y Construcción de la Práctica Docente II</t>
+          <t>Didáctica de la Matemática 2</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
@@ -1833,17 +1833,44 @@
         <v/>
       </c>
     </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>📌 TRAMO SUPERIOR / SEMINARIOS</t>
-        </is>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>Construcción de la Práctica Docente 1</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E41" s="10">
+        <f>IF(B41="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F41" s="10">
+        <f>IF(C41="SI", "APROBADO", IF(B41="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G41" s="11">
+        <f>IF(C41="SI", "🟢 Aprobada", IF(B41="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>Seminario de Especialización en Matemática</t>
+          <t>Reflexión y actualización de la práctica docente</t>
         </is>
       </c>
       <c r="B42" s="9" t="inlineStr">
@@ -1858,7 +1885,7 @@
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>Tramo Superior / Seminarios</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E42" s="10">
@@ -1877,7 +1904,7 @@
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>Epistemología de la Matemática</t>
+          <t>Esi</t>
         </is>
       </c>
       <c r="B43" s="9" t="inlineStr">
@@ -1892,7 +1919,7 @@
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>Tramo Superior / Seminarios</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E43" s="10">
@@ -1908,60 +1935,203 @@
         <v/>
       </c>
     </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="8" t="inlineStr">
-        <is>
-          <t>Taller de Investigación Educativa en Matemática</t>
-        </is>
-      </c>
-      <c r="B44" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C44" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D44" s="10" t="inlineStr">
-        <is>
-          <t>Tramo Superior / Seminarios</t>
-        </is>
-      </c>
-      <c r="E44" s="10">
-        <f>IF(B44="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F44" s="10">
-        <f>IF(C44="SI", "APROBADO", IF(B44="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G44" s="11">
-        <f>IF(C44="SI", "🟢 Aprobada", IF(B44="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>📌 5° AÑO</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>Construcción de la Práctica Docente 2</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E45" s="10">
+        <f>IF(B45="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F45" s="10">
+        <f>IF(C45="SI", "APROBADO", IF(B45="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G45" s="11">
+        <f>IF(C45="SI", "🟢 Aprobada", IF(B45="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>Temas avanzados de matemática</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E46" s="10">
+        <f>IF(B46="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F46" s="10">
+        <f>IF(C46="SI", "APROBADO", IF(B46="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G46" s="11">
+        <f>IF(C46="SI", "🟢 Aprobada", IF(B46="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>Fundamentos de la física</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E47" s="10">
+        <f>IF(B47="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F47" s="10">
+        <f>IF(C47="SI", "APROBADO", IF(B47="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G47" s="11">
+        <f>IF(C47="SI", "🟢 Aprobada", IF(B47="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>Análisis Matemático III</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E48" s="10">
+        <f>IF(B48="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F48" s="10">
+        <f>IF(C48="SI", "APROBADO", IF(B48="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G48" s="11">
+        <f>IF(C48="SI", "🟢 Aprobada", IF(B48="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>Astronomía superior</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E49" s="10">
+        <f>IF(B49="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F49" s="10">
+        <f>IF(C49="SI", "APROBADO", IF(B49="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G49" s="11">
+        <f>IF(C49="SI", "🟢 Aprobada", IF(B49="SI", "🟡 Regular", "🟣 Pendiente"))</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="A44:G44"/>
     <mergeCell ref="I12:J12"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="I15:J15"/>
     <mergeCell ref="I10:J10"/>
+    <mergeCell ref="A35:G35"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="I11:J11"/>
+    <mergeCell ref="A16:G16"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A25:G25"/>
     <mergeCell ref="I9:J9"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A23:G23"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B13 B15 B16 B17 B18 B19 B20 B21 B22 B24 B25 B26 B27 B28 B29 B30 B31 B33 B34 B35 B36 B37 B38 B39 B40 B42 B43 B44 C6 C7 C8 C9 C10 C11 C12 C13 C15 C16 C17 C18 C19 C20 C21 C22 C24 C25 C26 C27 C28 C29 C30 C31 C33 C34 C35 C36 C37 C38 C39 C40 C42 C43 C44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
+    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B17 B18 B19 B20 B21 B22 B23 B24 B26 B27 B28 B29 B30 B31 B32 B33 B34 B36 B37 B38 B39 B40 B41 B42 B43 B45 B46 B47 B48 B49 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C17 C18 C19 C20 C21 C22 C23 C24 C26 C27 C28 C29 C30 C31 C32 C33 C34 C36 C37 C38 C39 C40 C41 C42 C43 C45 C46 C47 C48 C49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
       <formula1>"SI,NO"</formula1>
     </dataValidation>
   </dataValidations>
